--- a/data-source/ESTOQUEQUIMICOSEADI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSEADI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/RELATÓRIOS QUIMICOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56A28647-AE54-4EAF-AA65-A1190EF3ABF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19FB222A-1E8A-4A04-A8E7-67A6F28B214D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{640A719B-EE02-4E60-B852-DCE1AC7E5E47}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96C22524-75C3-4BD9-A766-CBBF248E35B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
-  <si>
-    <t/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>Desc.completa</t>
+  </si>
+  <si>
+    <t>Qtd.física</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Familia</t>
   </si>
   <si>
     <t>RESINA LX-50B (AMERICA ASIA)</t>
@@ -56,36 +68,25 @@
     <t>RESINA MJ0055N (AMERICA ASIA)</t>
   </si>
   <si>
+    <t>ST-430 ANTIBACTERIAL AND ANTFUNGAL AGENTS</t>
+  </si>
+  <si>
     <t>RESINA LR-02 (AMERICA ASIA)</t>
   </si>
   <si>
+    <t>ANTIFUNGO</t>
+  </si>
+  <si>
     <t>RESINA FU6080 (AMERICA ASIA)</t>
-  </si>
-  <si>
-    <t>Produto</t>
-  </si>
-  <si>
-    <t>Cód.altern.1</t>
-  </si>
-  <si>
-    <t>Desc.completa</t>
-  </si>
-  <si>
-    <t>Qtd.física</t>
-  </si>
-  <si>
-    <t>Grupo</t>
-  </si>
-  <si>
-    <t>Familia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[Blue]###########0;[Red]\-###########0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -100,7 +101,6 @@
       <sz val="11"/>
       <color rgb="FF800000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -116,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -139,28 +139,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,130 +484,134 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99FDCF56-F56C-4E5B-842C-8BEB3590062D}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="5.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2903F38-B1EA-4C5D-A391-B75B6F841B7A}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>11370</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4">
+        <v>10080</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>16336</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C3" s="4">
+        <v>3060</v>
+      </c>
+      <c r="D3">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>11372</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C4">
+        <v>1800</v>
+      </c>
+      <c r="D4">
         <v>9</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>11612</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>11379</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="C6">
+        <v>3060</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>16684</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>11370</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>10080</v>
-      </c>
-      <c r="E2">
+      <c r="C7">
+        <v>2340</v>
+      </c>
+      <c r="D7">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>16336</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>3060</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>11372</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>1800</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>11379</v>
-      </c>
-      <c r="B5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>3060</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>16684</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E7" t="s">
         <v>6</v>
-      </c>
-      <c r="D6">
-        <v>2340</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/ESTOQUEQUIMICOSEADI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSEADI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19FB222A-1E8A-4A04-A8E7-67A6F28B214D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{19FB222A-1E8A-4A04-A8E7-67A6F28B214D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95E6CF6E-FF8A-4300-A1B2-AE57DC6D8798}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96C22524-75C3-4BD9-A766-CBBF248E35B7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Produto</t>
   </si>
@@ -62,9 +62,6 @@
     <t>RESINA IMPORTADA</t>
   </si>
   <si>
-    <t>RESINA LX-30B (AMERICA ASIA)</t>
-  </si>
-  <si>
     <t>RESINA MJ0055N (AMERICA ASIA)</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
   </si>
   <si>
     <t>ANTIFUNGO</t>
-  </si>
-  <si>
-    <t>RESINA FU6080 (AMERICA ASIA)</t>
   </si>
 </sst>
 </file>
@@ -485,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2903F38-B1EA-4C5D-A391-B75B6F841B7A}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -520,7 +514,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="4">
-        <v>10080</v>
+        <v>7380</v>
       </c>
       <c r="D2">
         <v>9</v>
@@ -531,13 +525,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>16336</v>
+        <v>11372</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
-        <v>3060</v>
+      <c r="C3">
+        <v>1800</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -548,69 +542,35 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>11372</v>
+        <v>11612</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>11612</v>
+        <v>11379</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>1620</v>
       </c>
       <c r="D5">
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>11379</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>3060</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>16684</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>2340</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
         <v>6</v>
       </c>
     </row>

--- a/data-source/ESTOQUEQUIMICOSEADI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSEADI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="8_{19FB222A-1E8A-4A04-A8E7-67A6F28B214D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95E6CF6E-FF8A-4300-A1B2-AE57DC6D8798}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96C22524-75C3-4BD9-A766-CBBF248E35B7}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="20736" windowHeight="11148" xr2:uid="{96C22524-75C3-4BD9-A766-CBBF248E35B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/data-source/ESTOQUEQUIMICOSEADI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSEADI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="8_{19FB222A-1E8A-4A04-A8E7-67A6F28B214D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95E6CF6E-FF8A-4300-A1B2-AE57DC6D8798}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="20736" windowHeight="11148" xr2:uid="{96C22524-75C3-4BD9-A766-CBBF248E35B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{96C22524-75C3-4BD9-A766-CBBF248E35B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/data-source/ESTOQUEQUIMICOSEADI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSEADI.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="8_{19FB222A-1E8A-4A04-A8E7-67A6F28B214D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95E6CF6E-FF8A-4300-A1B2-AE57DC6D8798}"/>
